--- a/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 7 (Coordinator told at expiry); T-78</t>
+          <t>E06-S05 — Scenario 7 (Coordinator told at expiry); T-79</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); T-78</t>
+          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); T-79</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">

--- a/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J315"/>
+  <dimension ref="A1:J316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16654,7 +16654,7 @@
         <is>
           <t>1. As an Event Coordinator permitted to view the event, open its Activity log
 2. Confirm no edit or delete control is offered for the entry
-3. For each existing application role (event_organiser, event_coordinator, venue_staff, technical_support and attendee), attempt direct API update and delete requests against the entry
+3. For each existing application role (event_organiser, event_coordinator, venue_staff, technical_support_staff and attendee), attempt direct API update and delete requests against the entry
 4. As the database test harness, attempt UPDATE and DELETE of that entry through the application database connection in separate transactions
 5. Read the original entry after each refused attempt to confirm its contents and row remain unchanged</t>
         </is>
@@ -16778,151 +16778,205 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
+          <t>E14-S02</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>E14-S02 - Scenario 1 (Status change recorded; access-denial entries not shown; T-75)</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>3 - Cross-cutting (data isolation)</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>TC_E14S02_08</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Verify that access-denial entries should not be shown in the event Activity log a Coordinator reads</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Event EVT-2003 belongs to Client B, is Under Review and is assigned to coord_b@connectsphere.com; organiser_a@clienta.com belongs to Client A; the database is a disposable test database seeded with `npm run db:seed:test --workspace backend`</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>1. As organiser_a@clienta.com, attempt to open EVT-2003 directly and confirm the request is refused
+2. As the tester, confirm in the test database that an "Access Denied" row naming organiser_a@clienta.com now exists for that attempt
+3. As coord_b@connectsphere.com, approve EVT-2003 so the log also holds a status-change entry
+4. As coord_b@connectsphere.com, open EVT-2003's Activity log
+5. Check every entry shown</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>Refused user: organiser_a@clienta.com (Organiser A, Client A) | Event: EVT-2003 (Client B) | Reader: coord_b@connectsphere.com</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>The Activity log shows the status-change entry from step 3 and no "Access Denied" entry; neither "Organiser A" nor organiser_a@clienta.com appears anywhere in the log</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C313" s="2" t="inlineStr">
+      <c r="C314" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D313" s="2" t="inlineStr">
+      <c r="D314" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E313" s="2" t="inlineStr">
+      <c r="E314" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_01</t>
         </is>
       </c>
-      <c r="F313" s="2" t="inlineStr">
+      <c r="F314" s="2" t="inlineStr">
         <is>
           <t>Verify a venue search returns within the 3-second target on a realistic catalogue</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr">
+      <c r="G314" s="2" t="inlineStr">
         <is>
           <t>The venue catalogue holds 50 venues with layouts, accessibility features and facilities. 200 confirmed bookings exist across the next 90 days. Coordinator coord_a@connectsphere.com is signed in</t>
         </is>
       </c>
-      <c r="H313" s="2" t="inlineStr">
+      <c r="H314" s="2" t="inlineStr">
         <is>
           <t>1. Open the venue search
  2. Enter date 2026-12-01, time 09:00–11:00, expected attendance 120, layout Theatre, accessibility Step-free access
  3. Start a timer on submit and stop it when results render</t>
         </is>
       </c>
-      <c r="I313" s="2" t="inlineStr">
+      <c r="I314" s="2" t="inlineStr">
         <is>
           <t>50 venues · 200 bookings · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J313" s="2" t="inlineStr">
+      <c r="J314" s="2" t="inlineStr">
         <is>
           <t>Results render in under 3 seconds. Record the measured time; if it exceeds 3 seconds the story does not meet the Definition of Done</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
+    <row r="315">
+      <c r="A315" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B314" s="2" t="inlineStr">
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C314" s="2" t="inlineStr">
+      <c r="C315" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D314" s="2" t="inlineStr">
+      <c r="D315" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E314" s="2" t="inlineStr">
+      <c r="E315" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_02</t>
         </is>
       </c>
-      <c r="F314" s="2" t="inlineStr">
+      <c r="F315" s="2" t="inlineStr">
         <is>
           <t>Verify the venue availability calendar loads within the 3-second target for a busy month</t>
         </is>
       </c>
-      <c r="G314" s="2" t="inlineStr">
+      <c r="G315" s="2" t="inlineStr">
         <is>
           <t>Orchid Hall has 40 confirmed bookings, 5 tentative holds and 3 maintenance blocks within 2026-12-01 to 2026-12-31</t>
         </is>
       </c>
-      <c r="H314" s="2" t="inlineStr">
+      <c r="H315" s="2" t="inlineStr">
         <is>
           <t>1. Open Orchid Hall in the venue catalogue
  2. Select the calendar for December 2026
  3. Start a timer on selection and stop it when all states have rendered</t>
         </is>
       </c>
-      <c r="I314" s="2" t="inlineStr">
+      <c r="I315" s="2" t="inlineStr">
         <is>
           <t>48 calendar entries in one month · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J314" s="2" t="inlineStr">
+      <c r="J315" s="2" t="inlineStr">
         <is>
           <t>The calendar renders all Free, Tentative, Confirmed and Blocked states in under 3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
+    <row r="316">
+      <c r="A316" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B315" s="2" t="inlineStr">
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>Definition of Done</t>
         </is>
       </c>
-      <c r="C315" s="2" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
         <is>
           <t>Definition of Done · BDR T-51 · Week 1 §8a</t>
         </is>
       </c>
-      <c r="D315" s="2" t="inlineStr">
+      <c r="D316" s="2" t="inlineStr">
         <is>
           <t>3 - Cross-cutting</t>
         </is>
       </c>
-      <c r="E315" s="2" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>TC_PERF_03</t>
         </is>
       </c>
-      <c r="F315" s="2" t="inlineStr">
+      <c r="F316" s="2" t="inlineStr">
         <is>
           <t>Verify a registration submission completes within the 3-second target near capacity</t>
         </is>
       </c>
-      <c r="G315" s="2" t="inlineStr">
+      <c r="G316" s="2" t="inlineStr">
         <is>
           <t>Event EVT-2001 is Confirmed with Orchid Hall booked, venue capacity 200, and 198 registrations recorded. Attendee attendee_b@example.com is signed in</t>
         </is>
       </c>
-      <c r="H315" s="2" t="inlineStr">
+      <c r="H316" s="2" t="inlineStr">
         <is>
           <t>1. Open event EVT-2001
  2. Submit a registration
  3. Start a timer on submit and stop it when confirmation renders</t>
         </is>
       </c>
-      <c r="I315" s="2" t="inlineStr">
+      <c r="I316" s="2" t="inlineStr">
         <is>
           <t>198 existing registrations · capacity 200 · elapsed time measured client-side</t>
         </is>
       </c>
-      <c r="J315" s="2" t="inlineStr">
+      <c r="J316" s="2" t="inlineStr">
         <is>
           <t>The registration is created and confirmation renders in under 3 seconds, including the capacity check against the booked venue</t>
         </is>

--- a/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
+++ b/docs/testing/PROJECT TEST CASES CAA 091026.xlsx
@@ -9312,7 +9312,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 7 (Coordinator told before and at expiry); assumes O-33</t>
+          <t>E06-S05 — Scenario 7 (Coordinator told at expiry); T-79</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Verify that the Coordinator should receive a reminder 24 hours before a hold expires and a notice when it expires</t>
+          <t>Verify that the Coordinator should receive one notice when a hold expires and no reminder before it</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Reminder at expiry minus 24h | Notice at expiry</t>
+          <t>No reminder at expiry minus 24h | One notice at expiry</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>After step 1 exactly one in-app notification and one email name "Riverside Hall", the event and the expiry time; after step 2 exactly one further notification and email say the hold has expired and the venue is free; step 3 produces nothing more</t>
+          <t>After step 1 there is no notification or email about the hold; after step 2 exactly one in-app notification and one email name "Riverside Hall", the event and the expiry time and say the hold has expired and the venue is free; step 3 produces nothing more</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); assumes O-34</t>
+          <t>E06-S05 — Scenario 8 (Venue Staff may extend a hold); T-79</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>Step 1 succeeds, the activity log records the extension by venue_staff_1, and the reminder is rescheduled to 06/01/2027 10:00; step 2 is refused with a message that an expired hold cannot be extended and must be placed again
+          <t>Step 1 succeeds and the activity log records the extension by venue_staff_1 with the old and new expiry; step 2 is refused with a message that an expired hold cannot be extended and must be placed again
 ## E06-S06</t>
         </is>
       </c>
